--- a/Game_Controller/Libraries/Components.xlsx
+++ b/Game_Controller/Libraries/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\morte\Documents\GitHub\engg3800-2026s2-team28\Game_Controller\Libraries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D99F88-67C7-412B-80F6-210914B65824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B90981-B068-4B6D-9439-2300058307B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Parts_DB" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="89">
   <si>
     <t>CID</t>
   </si>
@@ -51,6 +52,9 @@
     <t>Manufacturer</t>
   </si>
   <si>
+    <t>Molex</t>
+  </si>
+  <si>
     <t>Yageo</t>
   </si>
   <si>
@@ -63,9 +67,6 @@
     <t>USB4515-GF-A</t>
   </si>
   <si>
-    <t>USB Connectors USB C Rec 6P SMT Mid Mnt 1.6mm</t>
-  </si>
-  <si>
     <t>GCT</t>
   </si>
   <si>
@@ -76,9 +77,6 @@
   </si>
   <si>
     <t>BQ24074RGTR</t>
-  </si>
-  <si>
-    <t>Battery Management Li-Ion Batt Chrgr &amp; Pwr-Path Mgmt IC</t>
   </si>
   <si>
     <t>CC0603JRX7R9BB104</t>
@@ -161,6 +159,162 @@
   </si>
   <si>
     <t>LED RED</t>
+  </si>
+  <si>
+    <t>TLV75533PDBVR</t>
+  </si>
+  <si>
+    <t>Murata</t>
+  </si>
+  <si>
+    <t>GRM188R61A106ME69D</t>
+  </si>
+  <si>
+    <t>10 uF ± 20% 
+10V X5R 
+0603</t>
+  </si>
+  <si>
+    <t>IC REG LINEAR 3.3V 500MA</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>NES Pushbutton</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>USB C PD Header</t>
+  </si>
+  <si>
+    <t>Littelfuse</t>
+  </si>
+  <si>
+    <t> 1210L050YR</t>
+  </si>
+  <si>
+    <t>PTC Slow Blow 500 mA</t>
+  </si>
+  <si>
+    <t>FUSE</t>
+  </si>
+  <si>
+    <t>Bourns</t>
+  </si>
+  <si>
+    <t>CR0603-FX-5101ELF</t>
+  </si>
+  <si>
+    <t>5.1k ± 1%
+100 mW 
+0603</t>
+  </si>
+  <si>
+    <t>Molex Connector</t>
+  </si>
+  <si>
+    <t>MOLEX_KK</t>
+  </si>
+  <si>
+    <t>ETSG</t>
+  </si>
+  <si>
+    <t>HC05</t>
+  </si>
+  <si>
+    <t>HC05 Bluetooth Module</t>
+  </si>
+  <si>
+    <t>ST Electronics</t>
+  </si>
+  <si>
+    <t>STM32L432KCU3TR</t>
+  </si>
+  <si>
+    <t>STM32 Ultra Low Power MCU</t>
+  </si>
+  <si>
+    <t>TE</t>
+  </si>
+  <si>
+    <t>1825910-6</t>
+  </si>
+  <si>
+    <t>PKLCS1212E2000-R1</t>
+  </si>
+  <si>
+    <t>PIEZO</t>
+  </si>
+  <si>
+    <t>BUZZER PIEZO</t>
+  </si>
+  <si>
+    <t>Battery Management System</t>
+  </si>
+  <si>
+    <t>Samtec</t>
+  </si>
+  <si>
+    <t>FTSH-105-01-L-DV-K</t>
+  </si>
+  <si>
+    <t>10 Pin Header</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Vishay</t>
+  </si>
+  <si>
+    <t>0R ± 1%
+25 mW 
+0204</t>
+  </si>
+  <si>
+    <t>LQFP48-7x7mm</t>
+  </si>
+  <si>
+    <t>STM32L433CCT6</t>
+  </si>
+  <si>
+    <t>SPST NO</t>
+  </si>
+  <si>
+    <t>USB_PD</t>
+  </si>
+  <si>
+    <t>0603_RES</t>
+  </si>
+  <si>
+    <t>0603_CAP</t>
+  </si>
+  <si>
+    <t>0154001.DRFP</t>
+  </si>
+  <si>
+    <t>SOT23-5</t>
+  </si>
+  <si>
+    <t>TACTILE_PB</t>
+  </si>
+  <si>
+    <t>B2B-PH-K-S</t>
+  </si>
+  <si>
+    <t>SNES_PB</t>
+  </si>
+  <si>
+    <t>SHF-105-01-L-D-TH</t>
+  </si>
+  <si>
+    <t>NES  Shoulder Pushbutton</t>
+  </si>
+  <si>
+    <t>SHOULDER_PB</t>
   </si>
 </sst>
 </file>
@@ -481,14 +635,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="50.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -527,13 +681,16 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
-        <v>11</v>
+      <c r="F2" t="s">
+        <v>78</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
@@ -550,9 +707,12 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="s">
@@ -564,16 +724,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>80</v>
       </c>
       <c r="G4" t="s">
         <v>14</v>
@@ -584,16 +747,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>79</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
@@ -604,16 +770,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>80</v>
       </c>
       <c r="G6" t="s">
         <v>14</v>
@@ -624,16 +793,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>79</v>
       </c>
       <c r="G7" t="s">
         <v>14</v>
@@ -644,16 +816,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>79</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
@@ -664,16 +839,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>80</v>
       </c>
       <c r="G9" t="s">
         <v>14</v>
@@ -684,16 +862,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>79</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
@@ -704,16 +885,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>79</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
@@ -724,16 +908,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
         <v>35</v>
       </c>
-      <c r="D12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>36</v>
+      <c r="F12" t="s">
+        <v>35</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
@@ -744,18 +931,366 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
         <v>39</v>
       </c>
-      <c r="E13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="D14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" t="s">
+        <v>83</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>79</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" t="s">
+        <v>86</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E28" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Game_Controller/Libraries/Components.xlsx
+++ b/Game_Controller/Libraries/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\morte\Documents\GitHub\engg3800-2026s2-team28\Game_Controller\Libraries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B90981-B068-4B6D-9439-2300058307B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E091D0E-6E7D-4FBC-9E82-0E61FFBAD7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Parts_DB" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="95">
   <si>
     <t>CID</t>
   </si>
@@ -315,6 +314,24 @@
   </si>
   <si>
     <t>SHOULDER_PB</t>
+  </si>
+  <si>
+    <t>SI2301CDS-T1-E3</t>
+  </si>
+  <si>
+    <t>P Channel MOSFET</t>
+  </si>
+  <si>
+    <t>BZX84C5V6-E3-08</t>
+  </si>
+  <si>
+    <t>5.6V Zener Diode</t>
+  </si>
+  <si>
+    <t>SOT23-3</t>
+  </si>
+  <si>
+    <t>Game_Controller.PcbLib</t>
   </si>
 </sst>
 </file>
@@ -635,16 +652,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="50.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -695,6 +712,9 @@
       <c r="G2" t="s">
         <v>14</v>
       </c>
+      <c r="H2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -718,6 +738,9 @@
       <c r="G3" t="s">
         <v>14</v>
       </c>
+      <c r="H3" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -741,6 +764,9 @@
       <c r="G4" t="s">
         <v>14</v>
       </c>
+      <c r="H4" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -764,6 +790,9 @@
       <c r="G5" t="s">
         <v>14</v>
       </c>
+      <c r="H5" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -787,6 +816,9 @@
       <c r="G6" t="s">
         <v>14</v>
       </c>
+      <c r="H6" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -810,6 +842,9 @@
       <c r="G7" t="s">
         <v>14</v>
       </c>
+      <c r="H7" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -833,6 +868,9 @@
       <c r="G8" t="s">
         <v>14</v>
       </c>
+      <c r="H8" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -856,6 +894,9 @@
       <c r="G9" t="s">
         <v>14</v>
       </c>
+      <c r="H9" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -879,6 +920,9 @@
       <c r="G10" t="s">
         <v>14</v>
       </c>
+      <c r="H10" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -902,6 +946,9 @@
       <c r="G11" t="s">
         <v>14</v>
       </c>
+      <c r="H11" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -925,6 +972,9 @@
       <c r="G12" t="s">
         <v>14</v>
       </c>
+      <c r="H12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -948,6 +998,9 @@
       <c r="G13" t="s">
         <v>14</v>
       </c>
+      <c r="H13" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -971,6 +1024,9 @@
       <c r="G14" t="s">
         <v>14</v>
       </c>
+      <c r="H14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -993,6 +1049,9 @@
       </c>
       <c r="G15" t="s">
         <v>14</v>
+      </c>
+      <c r="H15" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -1017,8 +1076,11 @@
       <c r="G16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1040,8 +1102,11 @@
       <c r="G17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1063,8 +1128,11 @@
       <c r="G18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1086,8 +1154,11 @@
       <c r="G19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1109,8 +1180,11 @@
       <c r="G20" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1132,8 +1206,11 @@
       <c r="G21" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1155,8 +1232,11 @@
       <c r="G22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1178,8 +1258,11 @@
       <c r="G23" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1201,8 +1284,11 @@
       <c r="G24" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1224,8 +1310,11 @@
       <c r="G25" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1247,8 +1336,11 @@
       <c r="G26" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1270,8 +1362,11 @@
       <c r="G27" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1292,6 +1387,61 @@
       </c>
       <c r="G28" t="s">
         <v>14</v>
+      </c>
+      <c r="H28" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" t="s">
+        <v>89</v>
+      </c>
+      <c r="F29" t="s">
+        <v>93</v>
+      </c>
+      <c r="G29" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" t="s">
+        <v>91</v>
+      </c>
+      <c r="F30" t="s">
+        <v>93</v>
+      </c>
+      <c r="G30" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Game_Controller/Libraries/Components.xlsx
+++ b/Game_Controller/Libraries/Components.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\morte\Documents\GitHub\engg3800-2026s2-team28\Game_Controller\Libraries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E091D0E-6E7D-4FBC-9E82-0E61FFBAD7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC6B834-3590-45FF-9AE5-A8C827332999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parts_DB" sheetId="1" r:id="rId1"/>
@@ -263,75 +263,75 @@
     <t>10 Pin Header</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>Vishay</t>
   </si>
   <si>
+    <t>LQFP48-7x7mm</t>
+  </si>
+  <si>
+    <t>STM32L433CCT6</t>
+  </si>
+  <si>
+    <t>SPST NO</t>
+  </si>
+  <si>
+    <t>USB_PD</t>
+  </si>
+  <si>
+    <t>0603_RES</t>
+  </si>
+  <si>
+    <t>0603_CAP</t>
+  </si>
+  <si>
+    <t>0154001.DRFP</t>
+  </si>
+  <si>
+    <t>SOT23-5</t>
+  </si>
+  <si>
+    <t>TACTILE_PB</t>
+  </si>
+  <si>
+    <t>B2B-PH-K-S</t>
+  </si>
+  <si>
+    <t>SNES_PB</t>
+  </si>
+  <si>
+    <t>SHF-105-01-L-D-TH</t>
+  </si>
+  <si>
+    <t>NES  Shoulder Pushbutton</t>
+  </si>
+  <si>
+    <t>SHOULDER_PB</t>
+  </si>
+  <si>
+    <t>SI2301CDS-T1-E3</t>
+  </si>
+  <si>
+    <t>P Channel MOSFET</t>
+  </si>
+  <si>
+    <t>BZX84C5V6-E3-08</t>
+  </si>
+  <si>
+    <t>5.6V Zener Diode</t>
+  </si>
+  <si>
+    <t>SOT23-3</t>
+  </si>
+  <si>
+    <t>Game_Controller.PcbLib</t>
+  </si>
+  <si>
     <t>0R ± 1%
-25 mW 
-0204</t>
-  </si>
-  <si>
-    <t>LQFP48-7x7mm</t>
-  </si>
-  <si>
-    <t>STM32L433CCT6</t>
-  </si>
-  <si>
-    <t>SPST NO</t>
-  </si>
-  <si>
-    <t>USB_PD</t>
-  </si>
-  <si>
-    <t>0603_RES</t>
-  </si>
-  <si>
-    <t>0603_CAP</t>
-  </si>
-  <si>
-    <t>0154001.DRFP</t>
-  </si>
-  <si>
-    <t>SOT23-5</t>
-  </si>
-  <si>
-    <t>TACTILE_PB</t>
-  </si>
-  <si>
-    <t>B2B-PH-K-S</t>
-  </si>
-  <si>
-    <t>SNES_PB</t>
-  </si>
-  <si>
-    <t>SHF-105-01-L-D-TH</t>
-  </si>
-  <si>
-    <t>NES  Shoulder Pushbutton</t>
-  </si>
-  <si>
-    <t>SHOULDER_PB</t>
-  </si>
-  <si>
-    <t>SI2301CDS-T1-E3</t>
-  </si>
-  <si>
-    <t>P Channel MOSFET</t>
-  </si>
-  <si>
-    <t>BZX84C5V6-E3-08</t>
-  </si>
-  <si>
-    <t>5.6V Zener Diode</t>
-  </si>
-  <si>
-    <t>SOT23-3</t>
-  </si>
-  <si>
-    <t>Game_Controller.PcbLib</t>
+100 mW
+0603</t>
+  </si>
+  <si>
+    <t>RC0603FR-070RL</t>
   </si>
 </sst>
 </file>
@@ -653,18 +653,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -690,7 +690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -707,16 +707,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -739,10 +739,10 @@
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -759,16 +759,16 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s">
         <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -785,16 +785,16 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -811,16 +811,16 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s">
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -837,16 +837,16 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s">
         <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -863,16 +863,16 @@
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -889,16 +889,16 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s">
         <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -915,16 +915,16 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -941,16 +941,16 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -973,10 +973,10 @@
         <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -999,10 +999,10 @@
         <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1019,16 +1019,16 @@
         <v>39</v>
       </c>
       <c r="F14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s">
         <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1045,16 +1045,16 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s">
         <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1071,16 +1071,16 @@
         <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G16" t="s">
         <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1097,16 +1097,16 @@
         <v>51</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s">
         <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1123,16 +1123,16 @@
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>55</v>
@@ -1149,16 +1149,16 @@
         <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1181,10 +1181,10 @@
         <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1207,10 +1207,10 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1221,22 +1221,22 @@
         <v>64</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
         <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1259,10 +1259,10 @@
         <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1285,36 +1285,36 @@
         <v>14</v>
       </c>
       <c r="H24" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s">
         <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1322,25 +1322,25 @@
         <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>71</v>
@@ -1357,16 +1357,16 @@
         <v>70</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s">
         <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1377,71 +1377,71 @@
         <v>44</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
         <v>46</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" t="s">
+        <v>89</v>
+      </c>
+      <c r="F30" t="s">
         <v>91</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E30" t="s">
-        <v>91</v>
-      </c>
-      <c r="F30" t="s">
-        <v>93</v>
-      </c>
       <c r="G30" t="s">
         <v>14</v>
       </c>
       <c r="H30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
